--- a/D. Model/Genetic Algorithm/c1.xlsx
+++ b/D. Model/Genetic Algorithm/c1.xlsx
@@ -95,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -110,6 +110,9 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -672,17 +675,17 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Breaded Fried Croaker Fish</t>
+          <t>Yellow Cornmeal</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>442.0</t>
+          <t>379.9</t>
         </is>
       </c>
     </row>
@@ -694,17 +697,17 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Cooked Broccoli Raab</t>
+          <t>King Vitaman Cereal</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>342.9</t>
         </is>
       </c>
     </row>
@@ -716,17 +719,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Canned Tomato Juice</t>
+          <t>Unsweetened Orange-Grapefruit Juice</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>64.5</t>
         </is>
       </c>
     </row>
@@ -738,17 +741,17 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Classic Sirloin Steak</t>
+          <t>Cooked Chickpeas</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>223.0</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>294.0</t>
+          <t>365.7</t>
         </is>
       </c>
     </row>
@@ -760,7 +763,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Toasted White Bread</t>
+          <t>Quaker Natural Granola</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -770,7 +773,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>439.5</t>
+          <t>618.0</t>
         </is>
       </c>
     </row>
@@ -782,17 +785,17 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Unsweetened Soymilk</t>
+          <t>Nonfat Milk</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>55.8</t>
         </is>
       </c>
     </row>
@@ -804,17 +807,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Enriched Semolina</t>
+          <t>Cheese Ravioli with Marinara</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>518.4</t>
+          <t>468.0</t>
         </is>
       </c>
     </row>
@@ -826,17 +829,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Toasted Rye Bread</t>
+          <t>Lowfat Cottage Cheese</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>335.1</t>
+          <t>108.0</t>
         </is>
       </c>
     </row>
@@ -848,17 +851,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Pear Nectar</t>
+          <t>Canned Blackberry Juice</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>114.0</t>
         </is>
       </c>
     </row>
@@ -870,7 +873,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Fat-Free Ready-to-Eat Chocolate Pudding</t>
+          <t>Apple Pie</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -880,7 +883,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>237.0</t>
         </is>
       </c>
     </row>
@@ -925,11 +928,11 @@
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>530.5</v>
+        <v>787.25</v>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -950,11 +953,11 @@
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>803.13</v>
+        <v>1039.48</v>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -975,11 +978,11 @@
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>943.52</v>
+        <v>690</v>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -1000,11 +1003,11 @@
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>93</v>
+        <v>237</v>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -1046,7 +1049,11 @@
           <t>Keterpenuhan (%)</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr"/>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1061,12 +1068,17 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>233.4</t>
+          <t>338.1</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>78.8%</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>⚠️ BELOW MIN</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1095,17 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
           <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1122,17 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>42.3%</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>⚠️ BELOW MIN</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1149,17 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>59.9</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>50.8%</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>⚠️ BELOW MIN</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1176,17 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
           <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1203,17 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
           <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1227,17 +1264,17 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>551.00</t>
+          <t>859.00</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>55.1%</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Poor</t>
+          <t>85.9%</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1254,15 +1291,15 @@
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>65.50</t>
+          <t>136.00</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>11.9%</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
+          <t>24.7%</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
         <is>
           <t>Poor</t>
         </is>
@@ -1281,7 +1318,7 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
@@ -1289,7 +1326,7 @@
           <t>100.0%</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E44" s="9" t="inlineStr">
         <is>
           <t>Excellent</t>
         </is>
@@ -1308,15 +1345,15 @@
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.0031</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
         <is>
           <t>Poor</t>
         </is>
@@ -1335,7 +1372,7 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -1343,7 +1380,7 @@
           <t>100.0%</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E46" s="9" t="inlineStr">
         <is>
           <t>Excellent</t>
         </is>
@@ -1362,7 +1399,7 @@
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>18.59</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -1370,7 +1407,7 @@
           <t>100.0%</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E47" s="9" t="inlineStr">
         <is>
           <t>Excellent</t>
         </is>
@@ -1389,17 +1426,17 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>258.00</t>
+          <t>364.00</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>64.5%</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>Poor</t>
+          <t>91.0%</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1453,7 @@
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
@@ -1424,7 +1461,7 @@
           <t>100.0%</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E49" s="9" t="inlineStr">
         <is>
           <t>Excellent</t>
         </is>
@@ -1443,7 +1480,7 @@
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>1024.00</t>
+          <t>1809.00</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
@@ -1451,7 +1488,7 @@
           <t>100.0%</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E50" s="9" t="inlineStr">
         <is>
           <t>Excellent</t>
         </is>
@@ -1470,15 +1507,15 @@
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>2120.00</t>
+          <t>2025.00</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>62.4%</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
+          <t>59.6%</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
         <is>
           <t>Poor</t>
         </is>
@@ -1497,7 +1534,7 @@
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
@@ -1505,7 +1542,7 @@
           <t>100.0%</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E52" s="9" t="inlineStr">
         <is>
           <t>Excellent</t>
         </is>
@@ -1524,7 +1561,7 @@
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>1882.00</t>
+          <t>3101.00</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
@@ -1532,7 +1569,7 @@
           <t>100.0%</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E53" s="9" t="inlineStr">
         <is>
           <t>Excellent</t>
         </is>
@@ -1551,17 +1588,17 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>31.6%</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Poor</t>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1615,7 @@
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.0067</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
@@ -1586,7 +1623,7 @@
           <t>100.0%</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E55" s="9" t="inlineStr">
         <is>
           <t>Excellent</t>
         </is>
@@ -1605,7 +1642,7 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
@@ -1613,7 +1650,7 @@
           <t>100.0%</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E56" s="9" t="inlineStr">
         <is>
           <t>Excellent</t>
         </is>
@@ -1632,7 +1669,7 @@
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
@@ -1640,7 +1677,7 @@
           <t>100.0%</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E57" s="9" t="inlineStr">
         <is>
           <t>Excellent</t>
         </is>
@@ -1659,7 +1696,7 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>26.79</t>
+          <t>26.23</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
@@ -1667,7 +1704,7 @@
           <t>100.0%</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E58" s="9" t="inlineStr">
         <is>
           <t>Excellent</t>
         </is>
@@ -1686,15 +1723,15 @@
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>65.5%</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
+          <t>61.1%</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
         <is>
           <t>Poor</t>
         </is>
@@ -1713,7 +1750,7 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
@@ -1721,7 +1758,7 @@
           <t>100.0%</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E60" s="9" t="inlineStr">
         <is>
           <t>Excellent</t>
         </is>
@@ -1740,17 +1777,17 @@
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>108.40</t>
+          <t>85.40</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>Excellent</t>
+          <t>94.9%</t>
+        </is>
+      </c>
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1804,7 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.0012</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
@@ -1775,7 +1812,7 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E62" s="9" t="inlineStr">
         <is>
           <t>Poor</t>
         </is>
@@ -1794,15 +1831,15 @@
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>28.7%</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
+          <t>60.8%</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="inlineStr">
         <is>
           <t>Poor</t>
         </is>
@@ -1821,17 +1858,17 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>Excellent</t>
+          <t>24.7%</t>
+        </is>
+      </c>
+      <c r="E64" s="9" t="inlineStr">
+        <is>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1848,15 +1885,15 @@
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>632.10</t>
+          <t>550.00</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>17.1%</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
+          <t>14.9%</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
         <is>
           <t>Poor</t>
         </is>
@@ -1875,17 +1912,17 @@
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>91.5%</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>Good</t>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
